--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>97857</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387579.0384740353</v>
+        <v>387579</v>
       </c>
       <c r="R2" t="n">
-        <v>6261055.780690269</v>
+        <v>6261056</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100138</v>
+        <v>100146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100146</v>
+        <v>100152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100152</v>
+        <v>100156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100156</v>
+        <v>100162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100162</v>
+        <v>100163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100163</v>
+        <v>100190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100190</v>
+        <v>100196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100196</v>
+        <v>100203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100203</v>
+        <v>100207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100207</v>
+        <v>100214</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>310409</v>
       </c>
       <c r="B2" t="n">
-        <v>100217</v>
+        <v>100222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37556-2023 artfynd.xlsx
+++ b/artfynd/A 37556-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Flora Halland</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/310409</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/312420</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62069116</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94486747</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,8 +1253,20 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103790364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>